--- a/data/trans_orig/IP07C02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C02-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>19471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>40907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56706</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44276</t>
+          <t>44122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>91897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>113894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110800</t>
+          <t>111724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133666</t>
+          <t>134988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210248</t>
+          <t>210485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242474</t>
+          <t>242146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67481</t>
+          <t>67652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89162</t>
+          <t>88563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71374</t>
+          <t>71551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94214</t>
+          <t>93631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144063</t>
+          <t>145121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174391</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>31788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33431</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45385</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62138</t>
+          <t>62205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140579</t>
+          <t>140317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167289</t>
+          <t>167296</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161542</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188731</t>
+          <t>188347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309188</t>
+          <t>308857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>349109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105469</t>
+          <t>106491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132490</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108056</t>
+          <t>107134</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133371</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220219</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259538</t>
+          <t>258693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>35068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26706</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>58161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61820</t>
+          <t>61005</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84318</t>
+          <t>84024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107817</t>
+          <t>108274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133230</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176350</t>
+          <t>175326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211532</t>
+          <t>209985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98282</t>
+          <t>98167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121726</t>
+          <t>121701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79661</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103919</t>
+          <t>103910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182159</t>
+          <t>185616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217520</t>
+          <t>218813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>30809</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>31483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>41219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58690</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>47696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67345</t>
+          <t>66024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100975</t>
+          <t>102073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>128628</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>152094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261726</t>
+          <t>260549</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304775</t>
+          <t>301516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>154998</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124779</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>153192</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>287343</t>
+          <t>289336</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>329999</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20972</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40434</t>
+          <t>40978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>33745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139743</t>
+          <t>140088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165258</t>
+          <t>164517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131679</t>
+          <t>131246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157078</t>
+          <t>156895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279860</t>
+          <t>276472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315157</t>
+          <t>313294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69314</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93797</t>
+          <t>93445</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66650</t>
+          <t>67030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>90942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140124</t>
+          <t>143521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175506</t>
+          <t>177572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>37171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58765</t>
+          <t>59292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87413</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105753</t>
+          <t>105830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>19282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32110</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35701</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53381</t>
+          <t>53190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198260</t>
+          <t>197602</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199001</t>
+          <t>200208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229629</t>
+          <t>229570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405306</t>
+          <t>404043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>447615</t>
+          <t>447020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,39%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>132564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>100008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>211836</t>
+          <t>211069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252046</t>
+          <t>251865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
